--- a/Financial Analysis/NPK.xlsx
+++ b/Financial Analysis/NPK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2E5A77-A938-4227-8164-7E18F956F03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC14F841-3804-4985-9409-995E0FDCABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{88633ADD-F41A-4D9F-B21C-3ACE153B475A}"/>
   </bookViews>
@@ -785,17 +785,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>93.73</v>
+        <v>127.5</v>
       </c>
       <c r="E3" s="5">
-        <v>45988</v>
+        <v>46071</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45988</v>
+        <v>46071</v>
       </c>
       <c r="G3" s="5">
-        <v>46060</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -815,7 +815,7 @@
       </c>
       <c r="D5" s="7">
         <f>D3*D4</f>
-        <v>674.85599999999999</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -857,7 +857,7 @@
       </c>
       <c r="D9" s="7">
         <f>D5-D8</f>
-        <v>707.15599999999995</v>
+        <v>950.3</v>
       </c>
     </row>
   </sheetData>
@@ -1259,35 +1259,35 @@
         <v>12</v>
       </c>
       <c r="G6" s="9">
-        <f>SUM(G3:G5)</f>
+        <f t="shared" ref="G6:N6" si="4">SUM(G3:G5)</f>
         <v>76.599999999999994</v>
       </c>
       <c r="H6" s="9">
-        <f>SUM(H3:H5)</f>
+        <f t="shared" si="4"/>
         <v>85.1</v>
       </c>
       <c r="I6" s="9">
-        <f>SUM(I3:I5)</f>
+        <f t="shared" si="4"/>
         <v>91.8</v>
       </c>
       <c r="J6" s="9">
-        <f>SUM(J3:J5)</f>
+        <f t="shared" si="4"/>
         <v>134.69999999999999</v>
       </c>
       <c r="K6" s="9">
-        <f>SUM(K3:K5)</f>
+        <f t="shared" si="4"/>
         <v>103.60000000000001</v>
       </c>
       <c r="L6" s="9">
-        <f>SUM(L3:L5)</f>
+        <f t="shared" si="4"/>
         <v>120.39999999999999</v>
       </c>
       <c r="M6" s="9">
-        <f>SUM(M3:M5)</f>
+        <f t="shared" si="4"/>
         <v>115.39999999999999</v>
       </c>
       <c r="N6" s="9">
-        <f>SUM(N3:N5)</f>
+        <f t="shared" si="4"/>
         <v>165.82999999999998</v>
       </c>
       <c r="W6" s="9">
@@ -1304,43 +1304,43 @@
         <v>505.2299999999999</v>
       </c>
       <c r="AA6" s="9">
-        <f t="shared" ref="AA6:AJ6" si="4">SUM(AA3:AA5)</f>
+        <f t="shared" ref="AA6:AJ6" si="5">SUM(AA3:AA5)</f>
         <v>588.1339999999999</v>
       </c>
       <c r="AB6" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>639.27973999999995</v>
       </c>
       <c r="AC6" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>669.02432419999991</v>
       </c>
       <c r="AD6" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>694.67008772600002</v>
       </c>
       <c r="AE6" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>715.56853465778011</v>
       </c>
       <c r="AF6" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>731.18439830515342</v>
       </c>
       <c r="AG6" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>747.15355185955093</v>
       </c>
       <c r="AH6" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>763.4843821904077</v>
       </c>
       <c r="AI6" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>780.18548813130008</v>
       </c>
       <c r="AJ6" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>797.26568627576194</v>
       </c>
     </row>
@@ -1392,39 +1392,39 @@
         <v>470.5071999999999</v>
       </c>
       <c r="AB7" s="7">
-        <f t="shared" ref="AB7:AJ7" si="5">AB6-AB8</f>
+        <f t="shared" ref="AB7:AJ7" si="6">AB6-AB8</f>
         <v>511.42379199999993</v>
       </c>
       <c r="AC7" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>535.21945935999997</v>
       </c>
       <c r="AD7" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>555.73607018079997</v>
       </c>
       <c r="AE7" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>572.45482772622404</v>
       </c>
       <c r="AF7" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>584.94751864412274</v>
       </c>
       <c r="AG7" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>597.72284148764072</v>
       </c>
       <c r="AH7" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>610.78750575232618</v>
       </c>
       <c r="AI7" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>624.14839050504008</v>
       </c>
       <c r="AJ7" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>637.81254902060959</v>
       </c>
     </row>
@@ -1433,31 +1433,31 @@
         <v>14</v>
       </c>
       <c r="G8" s="9">
-        <f>G6-G7</f>
+        <f t="shared" ref="G8:M8" si="7">G6-G7</f>
         <v>13.799999999999997</v>
       </c>
       <c r="H8" s="9">
-        <f>H6-H7</f>
+        <f t="shared" si="7"/>
         <v>14.699999999999989</v>
       </c>
       <c r="I8" s="9">
-        <f>I6-I7</f>
+        <f t="shared" si="7"/>
         <v>17.200000000000003</v>
       </c>
       <c r="J8" s="9">
-        <f>J6-J7</f>
+        <f t="shared" si="7"/>
         <v>32.799999999999997</v>
       </c>
       <c r="K8" s="9">
-        <f>K6-K7</f>
+        <f t="shared" si="7"/>
         <v>18.100000000000009</v>
       </c>
       <c r="L8" s="9">
-        <f>L6-L7</f>
+        <f t="shared" si="7"/>
         <v>18.499999999999986</v>
       </c>
       <c r="M8" s="9">
-        <f>M6-M7</f>
+        <f t="shared" si="7"/>
         <v>15.899999999999991</v>
       </c>
       <c r="N8" s="9">
@@ -1485,39 +1485,39 @@
         <v>117.62679999999999</v>
       </c>
       <c r="AB8" s="9">
-        <f t="shared" ref="AB8:AJ8" si="6">AB6*0.2</f>
+        <f t="shared" ref="AB8:AJ8" si="8">AB6*0.2</f>
         <v>127.855948</v>
       </c>
       <c r="AC8" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>133.80486483999999</v>
       </c>
       <c r="AD8" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>138.93401754520002</v>
       </c>
       <c r="AE8" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>143.11370693155604</v>
       </c>
       <c r="AF8" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>146.23687966103068</v>
       </c>
       <c r="AG8" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>149.43071037191018</v>
       </c>
       <c r="AH8" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>152.69687643808155</v>
       </c>
       <c r="AI8" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>156.03709762626002</v>
       </c>
       <c r="AJ8" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>159.4531372551524</v>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
         <v>7.6</v>
       </c>
       <c r="J9" s="10">
-        <f t="shared" ref="J9:J11" si="7">Y9-I9-H9-G9</f>
+        <f t="shared" ref="J9:J11" si="9">Y9-I9-H9-G9</f>
         <v>9.0000000000000036</v>
       </c>
       <c r="K9" s="7">
@@ -1561,7 +1561,7 @@
         <v>31.8</v>
       </c>
       <c r="Z9" s="10">
-        <f t="shared" ref="Z9:Z11" si="8">SUM(K9:N9)</f>
+        <f t="shared" ref="Z9:Z11" si="10">SUM(K9:N9)</f>
         <v>37.2498</v>
       </c>
       <c r="AA9" s="7">
@@ -1569,39 +1569,39 @@
         <v>41.169379999999997</v>
       </c>
       <c r="AB9" s="7">
-        <f t="shared" ref="AB9:AJ9" si="9">AB6*0.07</f>
+        <f t="shared" ref="AB9:AJ9" si="11">AB6*0.07</f>
         <v>44.749581800000001</v>
       </c>
       <c r="AC9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>46.831702694000001</v>
       </c>
       <c r="AD9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>48.626906140820005</v>
       </c>
       <c r="AE9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>50.089797426044612</v>
       </c>
       <c r="AF9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>51.182907881360741</v>
       </c>
       <c r="AG9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>52.30074863016857</v>
       </c>
       <c r="AH9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>53.443906753328541</v>
       </c>
       <c r="AI9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>54.612984169191009</v>
       </c>
       <c r="AJ9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>55.808598039303341</v>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K10" s="7">
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2.7</v>
       </c>
       <c r="AA10" s="7">
@@ -1692,7 +1692,7 @@
         <v>0.4</v>
       </c>
       <c r="J11" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="K11" s="7">
@@ -1717,7 +1717,7 @@
         <v>1.5</v>
       </c>
       <c r="Z11" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA11" s="7">
@@ -1756,35 +1756,35 @@
         <v>18</v>
       </c>
       <c r="G12" s="9">
-        <f>G8-G9-G10-G11</f>
+        <f t="shared" ref="G12:N12" si="12">G8-G9-G10-G11</f>
         <v>6.1999999999999966</v>
       </c>
       <c r="H12" s="9">
-        <f>H8-H9-H10-H11</f>
+        <f t="shared" si="12"/>
         <v>6.2999999999999883</v>
       </c>
       <c r="I12" s="9">
-        <f>I8-I9-I10-I11</f>
+        <f t="shared" si="12"/>
         <v>9.2000000000000028</v>
       </c>
       <c r="J12" s="9">
-        <f>J8-J9-J10-J11</f>
+        <f t="shared" si="12"/>
         <v>23.499999999999993</v>
       </c>
       <c r="K12" s="9">
-        <f>K8-K9-K10-K11</f>
+        <f t="shared" si="12"/>
         <v>9.0000000000000089</v>
       </c>
       <c r="L12" s="9">
-        <f>L8-L9-L10-L11</f>
+        <f t="shared" si="12"/>
         <v>5.9999999999999849</v>
       </c>
       <c r="M12" s="9">
-        <f>M8-M9-M10-M11</f>
+        <f t="shared" si="12"/>
         <v>6.2999999999999918</v>
       </c>
       <c r="N12" s="9">
-        <f>N8-N9-N10-N11</f>
+        <f t="shared" si="12"/>
         <v>31.5077</v>
       </c>
       <c r="W12" s="9">
@@ -1808,39 +1808,39 @@
         <v>76.457419999999985</v>
       </c>
       <c r="AB12" s="9">
-        <f t="shared" ref="AB12:AJ12" si="10">AB8-AB9-AB10-AB11</f>
+        <f t="shared" ref="AB12:AJ12" si="13">AB8-AB9-AB10-AB11</f>
         <v>83.106366199999997</v>
       </c>
       <c r="AC12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>86.973162145999993</v>
       </c>
       <c r="AD12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>90.307111404380009</v>
       </c>
       <c r="AE12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>93.023909505511426</v>
       </c>
       <c r="AF12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>95.053971779669951</v>
       </c>
       <c r="AG12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>97.12996174174161</v>
       </c>
       <c r="AH12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>99.252969684752998</v>
       </c>
       <c r="AI12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>101.42411345706901</v>
       </c>
       <c r="AJ12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>103.64453921584905</v>
       </c>
     </row>
@@ -1891,39 +1891,39 @@
         <v>-1.6800000000000002</v>
       </c>
       <c r="AB13" s="7">
-        <f t="shared" ref="AB13:AJ13" si="11">AA13*1.05</f>
+        <f t="shared" ref="AB13:AJ13" si="14">AA13*1.05</f>
         <v>-1.7640000000000002</v>
       </c>
       <c r="AC13" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-1.8522000000000003</v>
       </c>
       <c r="AD13" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-1.9448100000000004</v>
       </c>
       <c r="AE13" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-2.0420505000000007</v>
       </c>
       <c r="AF13" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-2.1441530250000009</v>
       </c>
       <c r="AG13" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-2.2513606762500009</v>
       </c>
       <c r="AH13" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-2.3639287100625013</v>
       </c>
       <c r="AI13" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-2.4821251455656266</v>
       </c>
       <c r="AJ13" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-2.6062314028439082</v>
       </c>
     </row>
@@ -1932,35 +1932,35 @@
         <v>20</v>
       </c>
       <c r="G14" s="9">
-        <f>G12-G13</f>
+        <f t="shared" ref="G14:N14" si="15">G12-G13</f>
         <v>8.2999999999999972</v>
       </c>
       <c r="H14" s="9">
-        <f>H12-H13</f>
+        <f t="shared" si="15"/>
         <v>7.7999999999999883</v>
       </c>
       <c r="I14" s="9">
-        <f>I12-I13</f>
+        <f t="shared" si="15"/>
         <v>10.400000000000002</v>
       </c>
       <c r="J14" s="9">
-        <f>J12-J13</f>
+        <f t="shared" si="15"/>
         <v>24.199999999999992</v>
       </c>
       <c r="K14" s="9">
-        <f>K12-K13</f>
+        <f t="shared" si="15"/>
         <v>9.7000000000000082</v>
       </c>
       <c r="L14" s="9">
-        <f>L12-L13</f>
+        <f t="shared" si="15"/>
         <v>6.4999999999999849</v>
       </c>
       <c r="M14" s="9">
-        <f>M12-M13</f>
+        <f t="shared" si="15"/>
         <v>6.6999999999999922</v>
       </c>
       <c r="N14" s="9">
-        <f>N12-N13</f>
+        <f t="shared" si="15"/>
         <v>31.5077</v>
       </c>
       <c r="W14" s="9">
@@ -1984,39 +1984,39 @@
         <v>78.137419999999992</v>
       </c>
       <c r="AB14" s="9">
-        <f t="shared" ref="AB14:AJ14" si="12">AB12-AB13</f>
+        <f t="shared" ref="AB14:AJ14" si="16">AB12-AB13</f>
         <v>84.870366199999992</v>
       </c>
       <c r="AC14" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>88.825362145999989</v>
       </c>
       <c r="AD14" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>92.251921404380013</v>
       </c>
       <c r="AE14" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>95.065960005511428</v>
       </c>
       <c r="AF14" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97.198124804669945</v>
       </c>
       <c r="AG14" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>99.381322417991612</v>
       </c>
       <c r="AH14" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>101.61689839481549</v>
       </c>
       <c r="AI14" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>103.90623860263464</v>
       </c>
       <c r="AJ14" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>106.25077061869295</v>
       </c>
     </row>
@@ -2068,39 +2068,39 @@
         <v>17.971606599999998</v>
       </c>
       <c r="AB15" s="7">
-        <f t="shared" ref="AB15:AJ15" si="13">AB14*0.23</f>
+        <f t="shared" ref="AB15:AJ15" si="17">AB14*0.23</f>
         <v>19.520184225999998</v>
       </c>
       <c r="AC15" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>20.42983329358</v>
       </c>
       <c r="AD15" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>21.217941923007405</v>
       </c>
       <c r="AE15" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>21.865170801267631</v>
       </c>
       <c r="AF15" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>22.355568705074088</v>
       </c>
       <c r="AG15" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>22.857704156138073</v>
       </c>
       <c r="AH15" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>23.371886630807566</v>
       </c>
       <c r="AI15" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>23.898434878605968</v>
       </c>
       <c r="AJ15" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>24.43767724229938</v>
       </c>
     </row>
@@ -2109,35 +2109,35 @@
         <v>22</v>
       </c>
       <c r="G16" s="9">
-        <f>G14-G15</f>
+        <f t="shared" ref="G16:N16" si="18">G14-G15</f>
         <v>6.4999999999999973</v>
       </c>
       <c r="H16" s="9">
-        <f>H14-H15</f>
+        <f t="shared" si="18"/>
         <v>5.9999999999999885</v>
       </c>
       <c r="I16" s="9">
-        <f>I14-I15</f>
+        <f t="shared" si="18"/>
         <v>8.1000000000000014</v>
       </c>
       <c r="J16" s="9">
-        <f>J14-J15</f>
+        <f t="shared" si="18"/>
         <v>20.899999999999991</v>
       </c>
       <c r="K16" s="9">
-        <f>K14-K15</f>
+        <f t="shared" si="18"/>
         <v>7.500000000000008</v>
       </c>
       <c r="L16" s="9">
-        <f>L14-L15</f>
+        <f t="shared" si="18"/>
         <v>4.9999999999999849</v>
       </c>
       <c r="M16" s="9">
-        <f>M14-M15</f>
+        <f t="shared" si="18"/>
         <v>5.1999999999999922</v>
       </c>
       <c r="N16" s="9">
-        <f>N14-N15</f>
+        <f t="shared" si="18"/>
         <v>24.260929000000001</v>
       </c>
       <c r="W16" s="9">
@@ -2161,39 +2161,39 @@
         <v>60.16581339999999</v>
       </c>
       <c r="AB16" s="9">
-        <f t="shared" ref="AB16:AJ16" si="14">AB14-AB15</f>
+        <f t="shared" ref="AB16:AJ16" si="19">AB14-AB15</f>
         <v>65.350181973999995</v>
       </c>
       <c r="AC16" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>68.395528852419986</v>
       </c>
       <c r="AD16" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>71.033979481372612</v>
       </c>
       <c r="AE16" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>73.20078920424379</v>
       </c>
       <c r="AF16" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>74.842556099595853</v>
       </c>
       <c r="AG16" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>76.523618261853542</v>
       </c>
       <c r="AH16" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>78.245011764007927</v>
       </c>
       <c r="AI16" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>80.007803724028676</v>
       </c>
       <c r="AJ16" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>81.813093376393567</v>
       </c>
       <c r="AK16" s="2">
@@ -2201,407 +2201,407 @@
         <v>80.994962442629628</v>
       </c>
       <c r="AL16" s="2">
-        <f t="shared" ref="AL16:CW16" si="15">AK16*(1+$AM$21)</f>
+        <f t="shared" ref="AL16:CW16" si="20">AK16*(1+$AM$21)</f>
         <v>80.185012818203333</v>
       </c>
       <c r="AM16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>79.383162690021294</v>
       </c>
       <c r="AN16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>78.58933106312108</v>
       </c>
       <c r="AO16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>77.80343775248987</v>
       </c>
       <c r="AP16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>77.025403374964966</v>
       </c>
       <c r="AQ16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>76.255149341215315</v>
       </c>
       <c r="AR16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>75.492597847803168</v>
       </c>
       <c r="AS16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>74.737671869325141</v>
       </c>
       <c r="AT16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>73.990295150631894</v>
       </c>
       <c r="AU16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>73.250392199125571</v>
       </c>
       <c r="AV16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>72.517888277134318</v>
       </c>
       <c r="AW16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>71.792709394362973</v>
       </c>
       <c r="AX16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>71.074782300419344</v>
       </c>
       <c r="AY16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>70.364034477415146</v>
       </c>
       <c r="AZ16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>69.660394132640988</v>
       </c>
       <c r="BA16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>68.963790191314573</v>
       </c>
       <c r="BB16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>68.274152289401428</v>
       </c>
       <c r="BC16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>67.591410766507408</v>
       </c>
       <c r="BD16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>66.915496658842329</v>
       </c>
       <c r="BE16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>66.246341692253907</v>
       </c>
       <c r="BF16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>65.583878275331372</v>
       </c>
       <c r="BG16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>64.928039492578051</v>
       </c>
       <c r="BH16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>64.278759097652269</v>
       </c>
       <c r="BI16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>63.635971506675745</v>
       </c>
       <c r="BJ16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>62.999611791608984</v>
       </c>
       <c r="BK16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>62.369615673692891</v>
       </c>
       <c r="BL16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>61.745919516955965</v>
       </c>
       <c r="BM16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>61.128460321786406</v>
       </c>
       <c r="BN16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>60.517175718568538</v>
       </c>
       <c r="BO16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>59.912003961382851</v>
       </c>
       <c r="BP16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>59.312883921769021</v>
       </c>
       <c r="BQ16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>58.71975508255133</v>
       </c>
       <c r="BR16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>58.132557531725816</v>
       </c>
       <c r="BS16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>57.551231956408557</v>
       </c>
       <c r="BT16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>56.975719636844474</v>
       </c>
       <c r="BU16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>56.405962440476031</v>
       </c>
       <c r="BV16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>55.841902816071268</v>
       </c>
       <c r="BW16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>55.283483787910555</v>
       </c>
       <c r="BX16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>54.730648950031451</v>
       </c>
       <c r="BY16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>54.183342460531136</v>
       </c>
       <c r="BZ16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>53.641509035925822</v>
       </c>
       <c r="CA16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>53.105093945566566</v>
       </c>
       <c r="CB16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>52.574043006110898</v>
       </c>
       <c r="CC16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>52.048302576049785</v>
       </c>
       <c r="CD16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>51.527819550289287</v>
       </c>
       <c r="CE16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>51.012541354786393</v>
       </c>
       <c r="CF16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>50.502415941238532</v>
       </c>
       <c r="CG16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>49.997391781826146</v>
       </c>
       <c r="CH16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>49.497417864007886</v>
       </c>
       <c r="CI16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>49.002443685367808</v>
       </c>
       <c r="CJ16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>48.512419248514128</v>
       </c>
       <c r="CK16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>48.027295056028983</v>
       </c>
       <c r="CL16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>47.547022105468692</v>
       </c>
       <c r="CM16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>47.071551884414006</v>
       </c>
       <c r="CN16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>46.600836365569869</v>
       </c>
       <c r="CO16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>46.134828001914173</v>
       </c>
       <c r="CP16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>45.673479721895028</v>
       </c>
       <c r="CQ16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>45.216744924676078</v>
       </c>
       <c r="CR16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>44.76457747542932</v>
       </c>
       <c r="CS16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>44.316931700675028</v>
       </c>
       <c r="CT16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>43.873762383668279</v>
       </c>
       <c r="CU16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>43.435024759831599</v>
       </c>
       <c r="CV16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>43.000674512233282</v>
       </c>
       <c r="CW16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>42.570667767110947</v>
       </c>
       <c r="CX16" s="2">
-        <f t="shared" ref="CX16:EH16" si="16">CW16*(1+$AM$21)</f>
+        <f t="shared" ref="CX16:EH16" si="21">CW16*(1+$AM$21)</f>
         <v>42.144961089439839</v>
       </c>
       <c r="CY16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>41.72351147854544</v>
       </c>
       <c r="CZ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>41.306276363759984</v>
       </c>
       <c r="DA16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>40.893213600122387</v>
       </c>
       <c r="DB16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>40.48428146412116</v>
       </c>
       <c r="DC16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>40.079438649479947</v>
       </c>
       <c r="DD16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>39.678644262985145</v>
       </c>
       <c r="DE16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>39.281857820355292</v>
       </c>
       <c r="DF16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>38.889039242151739</v>
       </c>
       <c r="DG16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>38.500148849730223</v>
       </c>
       <c r="DH16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>38.115147361232921</v>
       </c>
       <c r="DI16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>37.733995887620594</v>
       </c>
       <c r="DJ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>37.356655928744388</v>
       </c>
       <c r="DK16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>36.983089369456941</v>
       </c>
       <c r="DL16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>36.613258475762372</v>
       </c>
       <c r="DM16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>36.24712589100475</v>
       </c>
       <c r="DN16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>35.884654632094701</v>
       </c>
       <c r="DO16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>35.525808085773754</v>
       </c>
       <c r="DP16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>35.170550004916016</v>
       </c>
       <c r="DQ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>34.818844504866853</v>
       </c>
       <c r="DR16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>34.470656059818182</v>
       </c>
       <c r="DS16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>34.125949499219999</v>
       </c>
       <c r="DT16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>33.784690004227798</v>
       </c>
       <c r="DU16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>33.446843104185518</v>
       </c>
       <c r="DV16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>33.112374673143663</v>
       </c>
       <c r="DW16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>32.781250926412227</v>
       </c>
       <c r="DX16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>32.453438417148107</v>
       </c>
       <c r="DY16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>32.128904032976628</v>
       </c>
       <c r="DZ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>31.807614992646862</v>
       </c>
       <c r="EA16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>31.489538842720393</v>
       </c>
       <c r="EB16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>31.174643454293189</v>
       </c>
       <c r="EC16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>30.862897019750257</v>
       </c>
       <c r="ED16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>30.554268049552753</v>
       </c>
       <c r="EE16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>30.248725369057226</v>
       </c>
       <c r="EF16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>29.946238115366654</v>
       </c>
       <c r="EG16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>29.646775734212987</v>
       </c>
       <c r="EH16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>29.350307976870859</v>
       </c>
     </row>
@@ -2681,35 +2681,35 @@
         <v>23</v>
       </c>
       <c r="G18" s="8">
-        <f>G16/G17</f>
+        <f t="shared" ref="G18:N18" si="22">G16/G17</f>
         <v>0.90277777777777735</v>
       </c>
       <c r="H18" s="8">
-        <f>H16/H17</f>
+        <f t="shared" si="22"/>
         <v>0.83333333333333171</v>
       </c>
       <c r="I18" s="8">
-        <f>I16/I17</f>
+        <f t="shared" si="22"/>
         <v>1.1250000000000002</v>
       </c>
       <c r="J18" s="8">
-        <f>J16/J17</f>
+        <f t="shared" si="22"/>
         <v>2.9027777777777763</v>
       </c>
       <c r="K18" s="8">
-        <f>K16/K17</f>
+        <f t="shared" si="22"/>
         <v>1.0416666666666679</v>
       </c>
       <c r="L18" s="8">
-        <f>L16/L17</f>
+        <f t="shared" si="22"/>
         <v>0.69444444444444231</v>
       </c>
       <c r="M18" s="8">
-        <f>M16/M17</f>
+        <f t="shared" si="22"/>
         <v>0.7222222222222211</v>
       </c>
       <c r="N18" s="8">
-        <f>N16/N17</f>
+        <f t="shared" si="22"/>
         <v>3.3695734722222221</v>
       </c>
       <c r="W18" s="8">
@@ -2733,39 +2733,39 @@
         <v>8.3563629722222199</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" ref="AB18:AJ18" si="17">AB16/AB17</f>
+        <f t="shared" ref="AB18:AJ18" si="23">AB16/AB17</f>
         <v>9.0764141630555546</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>9.4993790072805542</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>9.8658304835239736</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>10.166776278367193</v>
       </c>
       <c r="AF18" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>10.394799458277202</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>10.628280314146325</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>10.867362745001101</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>11.112194961670649</v>
       </c>
       <c r="AJ18" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>11.362929635610218</v>
       </c>
     </row>
@@ -2774,71 +2774,71 @@
         <v>47</v>
       </c>
       <c r="K20" s="11">
-        <f t="shared" ref="K20:K22" si="18">K3/G3-1</f>
+        <f t="shared" ref="K20:K22" si="24">K3/G3-1</f>
         <v>0.47090909090909094</v>
       </c>
       <c r="L20" s="11">
-        <f t="shared" ref="L20:L22" si="19">L3/H3-1</f>
+        <f t="shared" ref="L20:L22" si="25">L3/H3-1</f>
         <v>0.50983358547655078</v>
       </c>
       <c r="M20" s="11">
-        <f t="shared" ref="M20:N22" si="20">M3/I3-1</f>
+        <f t="shared" ref="M20:N22" si="26">M3/I3-1</f>
         <v>0.38622754491017952</v>
       </c>
       <c r="N20" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="X20" s="11">
-        <f t="shared" ref="X20:Y20" si="21">X3/W3-1</f>
+        <f t="shared" ref="X20:Y20" si="27">X3/W3-1</f>
         <v>0.19358024691358011</v>
       </c>
       <c r="Y20" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.17501034340091026</v>
       </c>
       <c r="Z20" s="11">
-        <f t="shared" ref="Z20:AJ20" si="22">Z3/Y3-1</f>
+        <f t="shared" ref="Z20:AJ20" si="28">Z3/Y3-1</f>
         <v>0.40221830985915474</v>
       </c>
       <c r="AA20" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AB20" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AC20" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AD20" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AE20" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF20" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG20" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH20" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI20" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ20" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -2847,71 +2847,71 @@
         <v>48</v>
       </c>
       <c r="K21" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>2.8169014084507005E-2</v>
       </c>
       <c r="L21" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>8.5561497326203328E-2</v>
       </c>
       <c r="M21" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>-9.2741935483870996E-2</v>
       </c>
       <c r="N21" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="X21" s="11">
-        <f t="shared" ref="X21:Y21" si="23">X4/W4-1</f>
+        <f t="shared" ref="X21:Y21" si="29">X4/W4-1</f>
         <v>-0.17497886728655965</v>
       </c>
       <c r="Y21" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>5.3278688524590168E-2</v>
       </c>
       <c r="Z21" s="11">
-        <f t="shared" ref="Z21:AJ21" si="24">Z4/Y4-1</f>
+        <f t="shared" ref="Z21:AJ21" si="30">Z4/Y4-1</f>
         <v>1.7509727626459082E-2</v>
       </c>
       <c r="AA21" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB21" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC21" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD21" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE21" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF21" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG21" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH21" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI21" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ21" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL21" s="1" t="s">
@@ -2926,78 +2926,78 @@
         <v>49</v>
       </c>
       <c r="K22" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1.666666666666667</v>
       </c>
       <c r="L22" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M22" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.49999999999999978</v>
       </c>
       <c r="N22" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.66666666666666696</v>
       </c>
       <c r="X22" s="11">
-        <f t="shared" ref="X22:Y22" si="25">X5/W5-1</f>
+        <f t="shared" ref="X22:Y22" si="31">X5/W5-1</f>
         <v>1</v>
       </c>
       <c r="Y22" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>-0.12500000000000011</v>
       </c>
       <c r="Z22" s="11">
-        <f t="shared" ref="Z22:AJ22" si="26">Z5/Y5-1</f>
+        <f t="shared" ref="Z22:AJ22" si="32">Z5/Y5-1</f>
         <v>0.71428571428571463</v>
       </c>
       <c r="AA22" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AB22" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AC22" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AD22" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE22" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AF22" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AG22" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AH22" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI22" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ22" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL22" s="1" t="s">
         <v>51</v>
       </c>
       <c r="AM22" s="11">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23" spans="2:39" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -3005,11 +3005,11 @@
         <v>42</v>
       </c>
       <c r="K23" s="12">
-        <f t="shared" ref="K23:L23" si="27">K6/G6-1</f>
+        <f t="shared" ref="K23:L23" si="33">K6/G6-1</f>
         <v>0.35248041775456951</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.41480611045828431</v>
       </c>
       <c r="M23" s="12">
@@ -3033,43 +3033,43 @@
         <v>0.30146831530139084</v>
       </c>
       <c r="AA23" s="12">
-        <f t="shared" ref="AA23:AJ23" si="28">AA6/Z6-1</f>
+        <f t="shared" ref="AA23:AJ23" si="34">AA6/Z6-1</f>
         <v>0.1640916018447045</v>
       </c>
       <c r="AB23" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>8.6962732982619695E-2</v>
       </c>
       <c r="AC23" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>4.6528276025140425E-2</v>
       </c>
       <c r="AD23" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8333080873653724E-2</v>
       </c>
       <c r="AE23" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.0083988501924841E-2</v>
       </c>
       <c r="AF23" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>2.1823016092849201E-2</v>
       </c>
       <c r="AG23" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>2.184011802140895E-2</v>
       </c>
       <c r="AH23" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>2.1857395029725613E-2</v>
       </c>
       <c r="AI23" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>2.1874849480191694E-2</v>
       </c>
       <c r="AJ23" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>2.1892483780199923E-2</v>
       </c>
       <c r="AL23" s="1" t="s">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AM23" s="7">
         <f>NPV(AM22,Z16:EH16)</f>
-        <v>628.89225513539532</v>
+        <v>693.98942870279075</v>
       </c>
     </row>
     <row r="24" spans="2:39" x14ac:dyDescent="0.3">
@@ -3085,27 +3085,27 @@
         <v>43</v>
       </c>
       <c r="G24" s="11">
-        <f t="shared" ref="G24:M24" si="29">G8/G6</f>
+        <f t="shared" ref="G24:L24" si="35">G8/G6</f>
         <v>0.18015665796344646</v>
       </c>
       <c r="H24" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0.17273795534665087</v>
       </c>
       <c r="I24" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0.187363834422658</v>
       </c>
       <c r="J24" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0.24350408314773569</v>
       </c>
       <c r="K24" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0.17471042471042478</v>
       </c>
       <c r="L24" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0.15365448504983378</v>
       </c>
       <c r="M24" s="11">
@@ -3117,11 +3117,11 @@
         <v>0.25</v>
       </c>
       <c r="W24" s="11">
-        <f t="shared" ref="W24:Y24" si="30">W8/W6</f>
+        <f t="shared" ref="W24:X24" si="36">W8/W6</f>
         <v>0.17133084577114432</v>
       </c>
       <c r="X24" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.19771193898503955</v>
       </c>
       <c r="Y24" s="11">
@@ -3133,43 +3133,43 @@
         <v>0.18596975634859358</v>
       </c>
       <c r="AA24" s="11">
-        <f t="shared" ref="AA24:AJ24" si="31">AA8/AA6</f>
+        <f t="shared" ref="AA24:AJ24" si="37">AA8/AA6</f>
         <v>0.2</v>
       </c>
       <c r="AB24" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.2</v>
       </c>
       <c r="AC24" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.2</v>
       </c>
       <c r="AD24" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.2</v>
       </c>
       <c r="AE24" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.2</v>
       </c>
       <c r="AF24" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.2</v>
       </c>
       <c r="AG24" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.19999999999999998</v>
       </c>
       <c r="AH24" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.2</v>
       </c>
       <c r="AI24" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.2</v>
       </c>
       <c r="AJ24" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.2</v>
       </c>
       <c r="AL24" s="1" t="s">
@@ -3185,27 +3185,27 @@
         <v>44</v>
       </c>
       <c r="G25" s="11">
-        <f t="shared" ref="G25:M25" si="32">G9/G6</f>
+        <f t="shared" ref="G25:L25" si="38">G9/G6</f>
         <v>9.3994778067885129E-2</v>
       </c>
       <c r="H25" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>9.400705052878966E-2</v>
       </c>
       <c r="I25" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>8.2788671023965144E-2</v>
       </c>
       <c r="J25" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>6.6815144766147028E-2</v>
       </c>
       <c r="K25" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>8.3976833976833962E-2</v>
       </c>
       <c r="L25" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>7.807308970099669E-2</v>
       </c>
       <c r="M25" s="11">
@@ -3217,11 +3217,11 @@
         <v>5.9999999999999991E-2</v>
       </c>
       <c r="W25" s="11">
-        <f t="shared" ref="W25:Y25" si="33">W9/W6</f>
+        <f t="shared" ref="W25:X25" si="39">W9/W6</f>
         <v>8.4266169154228854E-2</v>
       </c>
       <c r="X25" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>9.034907597535935E-2</v>
       </c>
       <c r="Y25" s="11">
@@ -3233,43 +3233,43 @@
         <v>7.3728400926310805E-2</v>
       </c>
       <c r="AA25" s="11">
-        <f t="shared" ref="AA25:AJ25" si="34">AA9/AA6</f>
+        <f t="shared" ref="AA25:AJ25" si="40">AA9/AA6</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AB25" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AC25" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AD25" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AE25" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AF25" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AG25" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AH25" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AI25" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AJ25" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AL25" s="1" t="s">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AM25" s="7">
         <f>AM23+AM24</f>
-        <v>596.59225513539536</v>
+        <v>661.68942870279079</v>
       </c>
     </row>
     <row r="26" spans="2:39" x14ac:dyDescent="0.3">
@@ -3285,27 +3285,27 @@
         <v>45</v>
       </c>
       <c r="G26" s="11">
-        <f t="shared" ref="G26:M26" si="35">G12/G6</f>
+        <f t="shared" ref="G26:L26" si="41">G12/G6</f>
         <v>8.0939947780678811E-2</v>
       </c>
       <c r="H26" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>7.403055229142172E-2</v>
       </c>
       <c r="I26" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>0.1002178649237473</v>
       </c>
       <c r="J26" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>0.17446176688938378</v>
       </c>
       <c r="K26" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>8.6872586872586949E-2</v>
       </c>
       <c r="L26" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>4.9833887043189244E-2</v>
       </c>
       <c r="M26" s="11">
@@ -3317,11 +3317,11 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="W26" s="11">
-        <f t="shared" ref="W26:Y26" si="36">W12/W6</f>
+        <f t="shared" ref="W26:X26" si="42">W12/W6</f>
         <v>6.8718905472636871E-2</v>
       </c>
       <c r="X26" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="42"/>
         <v>0.10266940451745374</v>
       </c>
       <c r="Y26" s="11">
@@ -3333,43 +3333,43 @@
         <v>0.10452209884606997</v>
       </c>
       <c r="AA26" s="11">
-        <f t="shared" ref="AA26:AJ26" si="37">AA12/AA6</f>
+        <f t="shared" ref="AA26:AJ26" si="43">AA12/AA6</f>
         <v>0.13</v>
       </c>
       <c r="AB26" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.13</v>
       </c>
       <c r="AC26" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.13</v>
       </c>
       <c r="AD26" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.13</v>
       </c>
       <c r="AE26" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.13</v>
       </c>
       <c r="AF26" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.13</v>
       </c>
       <c r="AG26" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.12999999999999998</v>
       </c>
       <c r="AH26" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.13</v>
       </c>
       <c r="AI26" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.13</v>
       </c>
       <c r="AJ26" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.13</v>
       </c>
       <c r="AL26" s="1" t="s">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="AM26" s="6">
         <f>AM25/AJ17</f>
-        <v>82.860035435471573</v>
+        <v>91.901309542054278</v>
       </c>
     </row>
     <row r="27" spans="2:39" x14ac:dyDescent="0.3">
@@ -3385,27 +3385,27 @@
         <v>21</v>
       </c>
       <c r="G27" s="11">
-        <f t="shared" ref="G27:M27" si="38">G15/G14</f>
+        <f t="shared" ref="G27:L27" si="44">G15/G14</f>
         <v>0.21686746987951816</v>
       </c>
       <c r="H27" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.23076923076923112</v>
       </c>
       <c r="I27" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.22115384615384609</v>
       </c>
       <c r="J27" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.13636363636363641</v>
       </c>
       <c r="K27" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.22680412371134004</v>
       </c>
       <c r="L27" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.23076923076923131</v>
       </c>
       <c r="M27" s="11">
@@ -3417,11 +3417,11 @@
         <v>0.23</v>
       </c>
       <c r="W27" s="11">
-        <f t="shared" ref="W27:Y27" si="39">W15/W14</f>
+        <f t="shared" ref="W27:X27" si="45">W15/W14</f>
         <v>0.20077220077220062</v>
       </c>
       <c r="X27" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v>0.18632075471698123</v>
       </c>
       <c r="Y27" s="11">
@@ -3433,43 +3433,43 @@
         <v>0.228768556656503</v>
       </c>
       <c r="AA27" s="11">
-        <f t="shared" ref="AA27:AJ27" si="40">AA15/AA14</f>
+        <f t="shared" ref="AA27:AJ27" si="46">AA15/AA14</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="AB27" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="AC27" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="AD27" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="AE27" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="AF27" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.23</v>
       </c>
       <c r="AG27" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="AH27" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="AI27" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.23</v>
       </c>
       <c r="AJ27" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.23</v>
       </c>
       <c r="AL27" s="1" t="s">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="AM27" s="6">
         <f>Main!D3</f>
-        <v>93.73</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="28" spans="2:39" x14ac:dyDescent="0.3">
@@ -3485,27 +3485,27 @@
         <v>46</v>
       </c>
       <c r="G28" s="11">
-        <f t="shared" ref="G28:M28" si="41">G16/G6</f>
+        <f t="shared" ref="G28:L28" si="47">G16/G6</f>
         <v>8.4856396866840697E-2</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>7.050528789659212E-2</v>
       </c>
       <c r="I28" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>8.8235294117647078E-2</v>
       </c>
       <c r="J28" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>0.15515961395694131</v>
       </c>
       <c r="K28" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>7.2393822393822471E-2</v>
       </c>
       <c r="L28" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>4.1528239202657684E-2</v>
       </c>
       <c r="M28" s="11">
@@ -3517,11 +3517,11 @@
         <v>0.14630000000000001</v>
       </c>
       <c r="W28" s="11">
-        <f t="shared" ref="W28:Y28" si="42">W16/W6</f>
+        <f t="shared" ref="W28:X28" si="48">W16/W6</f>
         <v>6.4365671641791106E-2</v>
       </c>
       <c r="X28" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>0.10120269873863297</v>
       </c>
       <c r="Y28" s="11">
@@ -3533,43 +3533,43 @@
         <v>8.3053122340320112E-2</v>
       </c>
       <c r="AA28" s="11">
-        <f t="shared" ref="AA28:AJ28" si="43">AA16/AA6</f>
+        <f t="shared" ref="AA28:AJ28" si="49">AA16/AA6</f>
         <v>0.10229949875368538</v>
       </c>
       <c r="AB28" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.10222470365477247</v>
       </c>
       <c r="AC28" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.10223175208794598</v>
       </c>
       <c r="AD28" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.10225570488273374</v>
       </c>
       <c r="AE28" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.10229738405036491</v>
       </c>
       <c r="AF28" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.10235797737626366</v>
       </c>
       <c r="AG28" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.10242020274332894</v>
       </c>
       <c r="AH28" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.10248410260800091</v>
       </c>
       <c r="AI28" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.10254972047181156</v>
       </c>
       <c r="AJ28" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.10261710090467342</v>
       </c>
       <c r="AL28" s="2" t="s">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AM28" s="12">
         <f>AM26/AM27-1</f>
-        <v>-0.11597102917452717</v>
+        <v>-0.27920541535643706</v>
       </c>
     </row>
     <row r="29" spans="2:39" x14ac:dyDescent="0.3">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="Z32" s="15">
         <f>Main!$D$9/Model!Z31</f>
-        <v>1.4036443032949582</v>
+        <v>1.8862643906312027</v>
       </c>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.3">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="Z33" s="11">
         <f>Z31/Main!$D$9-1</f>
-        <v>-0.28756879670115221</v>
+        <v>-0.46985162580237816</v>
       </c>
     </row>
   </sheetData>
